--- a/output/大阪兵庫奈良和歌山_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/大阪兵庫奈良和歌山_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
